--- a/data/trans_dic/P1413-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1413-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,64</t>
+          <t>12,1; 17,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 14,04</t>
+          <t>8,75; 14,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 11,69</t>
+          <t>7,0; 11,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,85; 22,83</t>
+          <t>16,49; 22,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,46; 18,62</t>
+          <t>13,5; 18,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,03; 24,39</t>
+          <t>17,66; 24,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,2; 17,85</t>
+          <t>12,04; 17,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,41; 33,85</t>
+          <t>28,19; 33,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,62; 17,4</t>
+          <t>13,52; 17,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,2; 18,15</t>
+          <t>14,08; 18,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 13,74</t>
+          <t>10,33; 13,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,72; 27,72</t>
+          <t>23,74; 27,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,91</t>
+          <t>11,32; 15,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,53</t>
+          <t>8,54; 12,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,65</t>
+          <t>6,24; 9,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 17,67</t>
+          <t>14,26; 19,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 22,53</t>
+          <t>17,32; 22,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,44; 20,02</t>
+          <t>15,05; 20,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,67</t>
+          <t>11,3; 15,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,79; 34,81</t>
+          <t>29,47; 34,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 18,44</t>
+          <t>14,96; 18,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,47; 15,68</t>
+          <t>12,42; 15,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 12,27</t>
+          <t>9,35; 12,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 25,27</t>
+          <t>22,77; 26,32</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,4; 23,45</t>
+          <t>17,33; 23,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,64</t>
+          <t>4,8; 8,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,55</t>
+          <t>4,68; 8,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 23,03</t>
+          <t>17,13; 23,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,11; 29,87</t>
+          <t>23,03; 29,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,27; 17,74</t>
+          <t>12,75; 17,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 13,05</t>
+          <t>8,45; 13,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,19; 76,51</t>
+          <t>29,82; 36,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 25,68</t>
+          <t>21,2; 25,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,43</t>
+          <t>9,32; 12,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,25</t>
+          <t>7,37; 10,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,03; 55,99</t>
+          <t>24,42; 28,68</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,36</t>
+          <t>14,85; 19,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,98</t>
+          <t>6,36; 10,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 11,23</t>
+          <t>7,5; 11,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,76; 22,02</t>
+          <t>16,3; 20,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 18,64</t>
+          <t>14,12; 18,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 21,86</t>
+          <t>16,81; 21,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 18,32</t>
+          <t>13,71; 18,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,06; 28,7</t>
+          <t>25,22; 29,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 18,24</t>
+          <t>14,93; 18,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 15,48</t>
+          <t>12,35; 15,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 14,58</t>
+          <t>11,35; 14,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,94; 24,57</t>
+          <t>21,71; 25,17</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,99; 17,44</t>
+          <t>14,99; 17,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 10,08</t>
+          <t>7,95; 10,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,16</t>
+          <t>7,25; 9,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,36</t>
+          <t>17,22; 20,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,82; 20,49</t>
+          <t>17,81; 20,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,94; 19,53</t>
+          <t>16,87; 19,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,78; 15,29</t>
+          <t>12,75; 15,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,25; 45,44</t>
+          <t>29,32; 31,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,88; 18,67</t>
+          <t>16,78; 18,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,84; 14,52</t>
+          <t>12,83; 14,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,33; 11,87</t>
+          <t>10,4; 11,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,91; 34,86</t>
+          <t>23,85; 25,64</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126378</t>
+          <t>135390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>209972</t>
+          <t>227620</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>336350</t>
+          <t>363011</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85990; 122450</t>
+          <t>83953; 124214</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63799; 98799</t>
+          <t>61541; 98720</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48569; 78910</t>
+          <t>47258; 75581</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107046; 145040</t>
+          <t>113893; 154146</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92630; 128194</t>
+          <t>92926; 129659</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>125701; 169984</t>
+          <t>123105; 168373</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82063; 120097</t>
+          <t>81040; 118592</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>191876; 228638</t>
+          <t>206564; 247307</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>188247; 240494</t>
+          <t>186921; 241178</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>198922; 254135</t>
+          <t>197217; 252622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137995; 185174</t>
+          <t>139179; 187021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>310880; 363293</t>
+          <t>337892; 391289</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158785</t>
+          <t>174790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>308890</t>
+          <t>343345</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>467675</t>
+          <t>518134</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>108925; 153059</t>
+          <t>108845; 151754</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88000; 127501</t>
+          <t>86933; 129111</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63722; 98671</t>
+          <t>63821; 100093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79315; 210167</t>
+          <t>149087; 198984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>166651; 218176</t>
+          <t>167717; 217290</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>158866; 206033</t>
+          <t>154820; 208334</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>117324; 163429</t>
+          <t>117805; 164965</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>285037; 333014</t>
+          <t>315187; 368985</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>288415; 355847</t>
+          <t>288783; 355141</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255264; 320881</t>
+          <t>254177; 319744</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>194060; 253334</t>
+          <t>193187; 252334</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>304249; 542406</t>
+          <t>481479; 556618</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140149</t>
+          <t>160737</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>434208</t>
+          <t>265568</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>574358</t>
+          <t>426305</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>118058; 159138</t>
+          <t>117610; 160785</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35383; 65479</t>
+          <t>36402; 64628</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38288; 64915</t>
+          <t>35555; 63320</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117831; 161923</t>
+          <t>137227; 186708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>158019; 204260</t>
+          <t>157480; 201228</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95377; 137901</t>
+          <t>99065; 138570</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67400; 102462</t>
+          <t>66318; 103128</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>281734; 714036</t>
+          <t>241977; 292637</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>288433; 349804</t>
+          <t>288866; 351803</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141786; 190798</t>
+          <t>142992; 192228</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>111684; 158253</t>
+          <t>113838; 158913</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>409599; 916111</t>
+          <t>393827; 462486</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176748</t>
+          <t>183360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>280594</t>
+          <t>305402</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>457342</t>
+          <t>488762</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>139647; 182415</t>
+          <t>139967; 183276</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58988; 94580</t>
+          <t>60235; 95215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69299; 105258</t>
+          <t>70319; 106807</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155198; 203894</t>
+          <t>161251; 206683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>145742; 193549</t>
+          <t>146620; 191589</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>177060; 229934</t>
+          <t>176817; 228279</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>142814; 191212</t>
+          <t>143060; 194188</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>229960; 313405</t>
+          <t>281831; 329958</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>294392; 361394</t>
+          <t>295742; 361111</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246917; 309628</t>
+          <t>246863; 310971</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>223973; 288863</t>
+          <t>224792; 284855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>402461; 495902</t>
+          <t>457295; 530188</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>602060</t>
+          <t>654276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1233663</t>
+          <t>1141936</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1835724</t>
+          <t>1796212</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>491205; 571470</t>
+          <t>491274; 578124</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>278887; 345582</t>
+          <t>272492; 346774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>246051; 310896</t>
+          <t>245974; 309842</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>465913; 668553</t>
+          <t>607107; 705157</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>602194; 692257</t>
+          <t>601826; 696772</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>602211; 694407</t>
+          <t>599804; 695235</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>453078; 541806</t>
+          <t>451864; 539195</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1069708; 1662016</t>
+          <t>1093870; 1190892</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1123590; 1242838</t>
+          <t>1116665; 1239970</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>896548; 1013551</t>
+          <t>895592; 1019284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>716938; 823410</t>
+          <t>721383; 829037</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1629138; 2479075</t>
+          <t>1731327; 1860958</t>
         </is>
       </c>
     </row>
